--- a/Functions and Code/Color Palette.xlsx
+++ b/Functions and Code/Color Palette.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/Functions and Code/Color Palette.xlsx
+++ b/Functions and Code/Color Palette.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yaleedu-my.sharepoint.com/personal/rebecca_ray_yale_edu/Documents/Documents/GitHub/matlabroot/Functions and Code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evynd\Documents\matlabroot\Functions and Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6EC13C-3921-7244-9FEF-4BB8A6C03E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7776905D-2D7B-4ABA-AA50-05242F167974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B90EF345-F11D-4BE8-9704-8686C964E4D8}"/>
+    <workbookView xWindow="-16200" yWindow="-45" windowWidth="16410" windowHeight="11550" xr2:uid="{B90EF345-F11D-4BE8-9704-8686C964E4D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="589">
   <si>
     <t>GreenYellow</t>
   </si>
@@ -1585,9 +1585,6 @@
     <t>VaporwaveYellow</t>
   </si>
   <si>
-    <t>VaporwaveGren</t>
-  </si>
-  <si>
     <t>VaporwavePink</t>
   </si>
   <si>
@@ -1658,6 +1655,144 @@
   </si>
   <si>
     <t>Grey</t>
+  </si>
+  <si>
+    <t>Wong Color Blind Friendly</t>
+  </si>
+  <si>
+    <t>#E69F00</t>
+  </si>
+  <si>
+    <t>230.159.0</t>
+  </si>
+  <si>
+    <t>86.180.233</t>
+  </si>
+  <si>
+    <t>0.158.115</t>
+  </si>
+  <si>
+    <t>240.228.66</t>
+  </si>
+  <si>
+    <t>0.114.178</t>
+  </si>
+  <si>
+    <t>WongOrange</t>
+  </si>
+  <si>
+    <t>WongBlue</t>
+  </si>
+  <si>
+    <t>WongYellow</t>
+  </si>
+  <si>
+    <t>WongGreen</t>
+  </si>
+  <si>
+    <t>WongLightBlue</t>
+  </si>
+  <si>
+    <t>213.94.0</t>
+  </si>
+  <si>
+    <t>WongPink</t>
+  </si>
+  <si>
+    <t>204.121.167</t>
+  </si>
+  <si>
+    <t>IBM Color Blind Friendly</t>
+  </si>
+  <si>
+    <t>100.143.255</t>
+  </si>
+  <si>
+    <t>#648FFF</t>
+  </si>
+  <si>
+    <t>IBMBlue</t>
+  </si>
+  <si>
+    <t>IBMPurple</t>
+  </si>
+  <si>
+    <t>IBMPink</t>
+  </si>
+  <si>
+    <t>IBMOrange</t>
+  </si>
+  <si>
+    <t>IBMYellow</t>
+  </si>
+  <si>
+    <t>#785EF0</t>
+  </si>
+  <si>
+    <t>#DC267F</t>
+  </si>
+  <si>
+    <t>#FE6100</t>
+  </si>
+  <si>
+    <t>#FFB000</t>
+  </si>
+  <si>
+    <t>255.176.0</t>
+  </si>
+  <si>
+    <t>254.97.0</t>
+  </si>
+  <si>
+    <t>220.38.127</t>
+  </si>
+  <si>
+    <t>120.94.240</t>
+  </si>
+  <si>
+    <t>#56B4E9</t>
+  </si>
+  <si>
+    <t>#009E73</t>
+  </si>
+  <si>
+    <t>#F0E442</t>
+  </si>
+  <si>
+    <t>#0072B2</t>
+  </si>
+  <si>
+    <t>#D55E00</t>
+  </si>
+  <si>
+    <t>#CC79A7</t>
+  </si>
+  <si>
+    <t>escape</t>
+  </si>
+  <si>
+    <t>jumps</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>sleep</t>
+  </si>
+  <si>
+    <t>courtship</t>
+  </si>
+  <si>
+    <t>food quadrant</t>
+  </si>
+  <si>
+    <t>fly on food</t>
+  </si>
+  <si>
+    <t>WongRed</t>
+  </si>
+  <si>
+    <t>VaporwaveGreen</t>
   </si>
 </sst>
 </file>
@@ -1710,7 +1845,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="185">
+  <fills count="197">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2812,6 +2947,78 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6666DD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE69F00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56B4E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF009E73"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0E442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0072B2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD55E00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC79A7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF648FFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF785EF0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC267F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFE6100"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3009,7 +3216,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3711,6 +3918,40 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="184" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="185" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="186" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="187" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="188" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="189" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="190" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="191" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="192" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="193" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="194" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="195" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="196" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3722,16 +3963,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF6666DD"/>
-      <color rgb="FFA5A5EB"/>
-      <color rgb="FFEBA5A5"/>
-      <color rgb="FFFF71CE"/>
-      <color rgb="FFFFA700"/>
-      <color rgb="FFD62D20"/>
-      <color rgb="FF0057E7"/>
-      <color rgb="FF008744"/>
-      <color rgb="FF8EC127"/>
-      <color rgb="FFD41243"/>
+      <color rgb="FFFFB000"/>
+      <color rgb="FFFE6100"/>
+      <color rgb="FFDC267F"/>
+      <color rgb="FF785EF0"/>
+      <color rgb="FF648FFF"/>
+      <color rgb="FFCC79A7"/>
+      <color rgb="FFD55E00"/>
+      <color rgb="FF0072B2"/>
+      <color rgb="FFF0E442"/>
+      <color rgb="FF009E73"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3746,9 +3987,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3786,7 +4027,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3892,7 +4133,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4034,7 +4275,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4042,7 +4283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBF5F8C-DD5F-4ED3-9E54-88EB7CF98784}">
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="24" bestFit="1" customWidth="1"/>
@@ -5771,7 +6012,7 @@
     </row>
     <row r="147" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="24" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B147" s="24">
         <v>808080</v>
@@ -5905,7 +6146,7 @@
         <v>432</v>
       </c>
       <c r="C158" s="170" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D158" s="203"/>
     </row>
@@ -5917,7 +6158,7 @@
         <v>433</v>
       </c>
       <c r="C159" s="170" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D159" s="204"/>
     </row>
@@ -5991,7 +6232,7 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B166" s="24" t="s">
         <v>507</v>
@@ -6003,7 +6244,7 @@
     </row>
     <row r="167" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B167" s="24" t="s">
         <v>508</v>
@@ -6015,7 +6256,7 @@
     </row>
     <row r="168" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="24" t="s">
-        <v>519</v>
+        <v>588</v>
       </c>
       <c r="B168" s="24" t="s">
         <v>509</v>
@@ -6255,7 +6496,7 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="199" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B189" s="199"/>
       <c r="C189" s="199"/>
@@ -6263,75 +6504,235 @@
     </row>
     <row r="190" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="24" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B190" s="24" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C190" s="170" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D190" s="239"/>
     </row>
     <row r="191" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="24" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B191" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C191" s="170" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D191" s="235"/>
     </row>
     <row r="192" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="24" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B192" s="24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C192" s="170" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D192" s="236"/>
     </row>
     <row r="193" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="24" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B193" s="24" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C193" s="170" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D193" s="237"/>
     </row>
     <row r="194" spans="1:4" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A194" s="24" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B194" s="24" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C194" s="170" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D194" s="238"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="24" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B195" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="C195" s="170" t="s">
         <v>528</v>
       </c>
-      <c r="C195" s="170" t="s">
-        <v>529</v>
-      </c>
       <c r="D195" s="240"/>
+    </row>
+    <row r="196" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="199" t="s">
+        <v>543</v>
+      </c>
+      <c r="B196" s="199"/>
+      <c r="C196" s="199"/>
+      <c r="D196" s="199"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="B197" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="C197" s="170" t="s">
+        <v>545</v>
+      </c>
+      <c r="D197" s="241"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="B198" s="24" t="s">
+        <v>574</v>
+      </c>
+      <c r="C198" s="170" t="s">
+        <v>546</v>
+      </c>
+      <c r="D198" s="242"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="B199" s="24" t="s">
+        <v>575</v>
+      </c>
+      <c r="C199" s="170" t="s">
+        <v>547</v>
+      </c>
+      <c r="D199" s="243"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="24" t="s">
+        <v>552</v>
+      </c>
+      <c r="B200" s="24" t="s">
+        <v>576</v>
+      </c>
+      <c r="C200" s="170" t="s">
+        <v>548</v>
+      </c>
+      <c r="D200" s="244"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="B201" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="C201" s="170" t="s">
+        <v>549</v>
+      </c>
+      <c r="D201" s="245"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="24" t="s">
+        <v>587</v>
+      </c>
+      <c r="B202" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="C202" s="170" t="s">
+        <v>555</v>
+      </c>
+      <c r="D202" s="246"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="B203" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="C203" s="170" t="s">
+        <v>557</v>
+      </c>
+      <c r="D203" s="247"/>
+    </row>
+    <row r="204" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="199" t="s">
+        <v>558</v>
+      </c>
+      <c r="B204" s="199"/>
+      <c r="C204" s="199"/>
+      <c r="D204" s="199"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="B205" s="170" t="s">
+        <v>560</v>
+      </c>
+      <c r="C205" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="D205" s="248"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="B206" s="24" t="s">
+        <v>566</v>
+      </c>
+      <c r="C206" s="170" t="s">
+        <v>573</v>
+      </c>
+      <c r="D206" s="249"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="B207" s="24" t="s">
+        <v>567</v>
+      </c>
+      <c r="C207" s="170" t="s">
+        <v>572</v>
+      </c>
+      <c r="D207" s="250"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="B208" s="24" t="s">
+        <v>568</v>
+      </c>
+      <c r="C208" s="170" t="s">
+        <v>571</v>
+      </c>
+      <c r="D208" s="251"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="B209" s="24" t="s">
+        <v>569</v>
+      </c>
+      <c r="C209" s="170" t="s">
+        <v>570</v>
+      </c>
+      <c r="D209" s="252"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7622,6 +8023,69 @@
       </c>
       <c r="E94" s="52"/>
     </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="24" t="s">
+        <v>552</v>
+      </c>
+      <c r="B99" s="244"/>
+      <c r="C99" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="B100" s="241"/>
+      <c r="C100" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="24" t="s">
+        <v>587</v>
+      </c>
+      <c r="B101" s="246"/>
+      <c r="C101" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="B102" s="243"/>
+      <c r="C102" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="B103" s="247"/>
+      <c r="C103" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="B104" s="245"/>
+      <c r="C104" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="B105" s="242"/>
+      <c r="C105" t="s">
+        <v>586</v>
+      </c>
+    </row>
     <row r="122" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E122" s="24"/>
       <c r="F122" s="24"/>
